--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484774_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484774_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1653</v>
+        <v>8.633100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9285</v>
+        <v>6.37</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2368</v>
+        <v>2.2631</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5722</v>
+        <v>6.943</v>
       </c>
       <c r="H2" t="n">
-        <v>4.838</v>
+        <v>8.1273</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7341</v>
+        <v>-1.1843</v>
       </c>
       <c r="J2" t="n">
-        <v>8.245900000000001</v>
+        <v>7.6382</v>
       </c>
       <c r="K2" t="n">
-        <v>4.971</v>
+        <v>8.1303</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2748</v>
+        <v>-0.4921</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6737</v>
+        <v>-0.6952</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.133</v>
+        <v>-0.0031</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5407</v>
+        <v>-0.6922</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.0192</v>
+        <v>-3.9627</v>
       </c>
       <c r="R2" t="n">
-        <v>3.774</v>
+        <v>3.9627</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8383</v>
+        <v>-1.1211</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0792</v>
+        <v>-0.0978</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2409</v>
+        <v>-1.0233</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.8112</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6226</v>
+        <v>2.7922</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6226</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.0312</v>
+        <v>7.7774</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6623</v>
+        <v>6.149</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3689</v>
+        <v>1.6284</v>
       </c>
       <c r="G3" t="n">
-        <v>6.943</v>
+        <v>7.5722</v>
       </c>
       <c r="H3" t="n">
-        <v>8.1273</v>
+        <v>4.838</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1843</v>
+        <v>2.7341</v>
       </c>
       <c r="J3" t="n">
-        <v>7.6382</v>
+        <v>8.245900000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>8.1303</v>
+        <v>4.971</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4921</v>
+        <v>3.2748</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6952</v>
+        <v>-0.6737</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0031</v>
+        <v>-0.133</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6922</v>
+        <v>-0.5407</v>
       </c>
       <c r="P3" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-3.0192</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.774</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.5496</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.8493000000000001</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-3.9627</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.9627</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.723</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.1945</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.9175</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.8112</v>
-      </c>
       <c r="W3" t="n">
-        <v>2.7922</v>
+        <v>0.6226</v>
       </c>
       <c r="X3" t="n">
-        <v>0.019</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.777</v>
+        <v>7.1054</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8543</v>
+        <v>5.3415</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9227</v>
+        <v>1.7639</v>
       </c>
       <c r="G4" t="n">
         <v>5.9664</v>
@@ -766,13 +766,13 @@
         <v>3.3966</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3026</v>
+        <v>-0.9742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8107</v>
+        <v>-0.3235</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4919</v>
+        <v>-0.6506</v>
       </c>
       <c r="V4" t="n">
         <v>1.547</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2013</v>
+        <v>4.8542</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8349</v>
+        <v>2.9323</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3664</v>
+        <v>1.9219</v>
       </c>
       <c r="G5" t="n">
         <v>1.4535</v>
@@ -844,13 +844,13 @@
         <v>3.774</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2714</v>
+        <v>-1.6185</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3963</v>
+        <v>-0.2988</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8752</v>
+        <v>-1.3196</v>
       </c>
       <c r="V5" t="n">
         <v>1.2452</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7592</v>
+        <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1308</v>
+        <v>2.8128</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3716</v>
+        <v>-0.2128</v>
       </c>
       <c r="G6" t="n">
         <v>2.6267</v>
@@ -922,13 +922,13 @@
         <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2449</v>
+        <v>-1.4042</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7519</v>
+        <v>-0.0699</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.493</v>
+        <v>-1.3343</v>
       </c>
       <c r="V6" t="n">
         <v>0.6226</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1931</v>
+        <v>-1.9634</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3467</v>
+        <v>-3.2493</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1536</v>
+        <v>1.2859</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8575</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5244</v>
+        <v>-0.2947</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1129</v>
+        <v>0.0194</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2169</v>
+        <v>-2.4828</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9609</v>
+        <v>-1.2532</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.256</v>
+        <v>-1.2295</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3179</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1011</v>
+        <v>-0.1648</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4144</v>
+        <v>0.1221</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3133</v>
+        <v>-0.2869</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>25.5581</v>
+        <v>25.558</v>
       </c>
       <c r="E10" t="n">
-        <v>18.9138</v>
+        <v>18.9137</v>
       </c>
       <c r="F10" t="n">
-        <v>6.644400000000001</v>
+        <v>6.6445</v>
       </c>
       <c r="G10" t="n">
         <v>21.9066</v>
@@ -1234,13 +1234,13 @@
         <v>19.8135</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.386699999999999</v>
+        <v>-6.3869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9762</v>
+        <v>-0.9762000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.4106</v>
+        <v>-5.410500000000001</v>
       </c>
       <c r="V10" t="n">
         <v>5.320600000000001</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1657</v>
+        <v>2.7471</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2198</v>
+        <v>2.8198</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.054</v>
+        <v>-0.0726</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0765</v>
+        <v>3.5427</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3885</v>
+        <v>-1.9948</v>
       </c>
       <c r="I11" t="n">
-        <v>0.312</v>
+        <v>5.5375</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6858</v>
+        <v>4.7581</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2052</v>
+        <v>0.2168</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4807</v>
+        <v>4.5413</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.7623</v>
+        <v>-1.2154</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.5936</v>
+        <v>-2.2116</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1687</v>
+        <v>0.9962</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0192</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8305</v>
+        <v>2.4531</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2613</v>
+        <v>0.4872</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3835</v>
+        <v>-0.0514</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1222</v>
+        <v>0.5385</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1696</v>
+        <v>-1.8488</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6345</v>
+        <v>0.9127</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9429</v>
+        <v>2.7839</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3084</v>
+        <v>-1.8712</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5427</v>
+        <v>-2.0765</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9948</v>
+        <v>-2.3885</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5375</v>
+        <v>0.312</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7581</v>
+        <v>2.6858</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2168</v>
+        <v>1.2052</v>
       </c>
       <c r="L12" t="n">
-        <v>4.5413</v>
+        <v>1.4807</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2154</v>
+        <v>-4.7623</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2116</v>
+        <v>-3.5936</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9962</v>
+        <v>-1.1687</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4531</v>
+        <v>2.8305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6254999999999999</v>
+        <v>1.0083</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9283</v>
+        <v>0.9477</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3028</v>
+        <v>0.0606</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8488</v>
+        <v>2.1696</v>
       </c>
       <c r="W12" t="n">
+        <v>2.1696</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.8488</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8952</v>
+        <v>-1.704</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2241</v>
+        <v>0.1267</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1193</v>
+        <v>-1.8307</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9744</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.947</v>
+        <v>1.1382</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3267</v>
+        <v>1.2293</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3797</v>
+        <v>-0.0911</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.2754</v>
+        <v>-2.9838</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3661</v>
+        <v>-0.3159</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6415</v>
+        <v>-2.6679</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8604000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1321</v>
+        <v>1.4236</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8558</v>
+        <v>1.1737</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2763</v>
+        <v>0.2498</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7922</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1593</v>
+        <v>-3.8057</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.1452</v>
+        <v>-1.9503</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0141</v>
+        <v>-1.8554</v>
       </c>
       <c r="G15" t="n">
         <v>-2.8513</v>
@@ -1624,13 +1624,13 @@
         <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5532</v>
+        <v>-0.1996</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5291</v>
+        <v>-0.3342</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0241</v>
+        <v>0.1346</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FERRIZ SELLES</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.4552</v>
+        <v>-4.1606</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3309</v>
+        <v>-2.6794</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1243</v>
+        <v>-1.4812</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.3159</v>
+        <v>-3.623</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-2.2672</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.3556</v>
+        <v>-1.3558</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8853</v>
+        <v>0.3054</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.9039</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2991</v>
+        <v>-0.5984</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4306</v>
+        <v>-3.9284</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3741</v>
+        <v>-3.171</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0565</v>
+        <v>-0.7574</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3774</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>-4.9062</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5661</v>
+        <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>0.238</v>
+        <v>1.1422</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4979</v>
+        <v>0.7141</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2598</v>
+        <v>0.428</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5846</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>A. FERRIZ SELLES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.241</v>
+        <v>-4.2604</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.2383</v>
+        <v>-2.1361</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0027</v>
+        <v>-2.1243</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.623</v>
+        <v>-4.3159</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2672</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3558</v>
+        <v>-3.3556</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3054</v>
+        <v>-1.8853</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9039</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5984</v>
+        <v>-1.2991</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9284</v>
+        <v>-2.4306</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.171</v>
+        <v>-0.3741</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7574</v>
+        <v>-2.0565</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2644</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.9062</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6418</v>
+        <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0618</v>
+        <v>0.4329</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8448</v>
+        <v>0.6927</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9066</v>
+        <v>-0.2598</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5846</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.6268</v>
+        <v>-5.6545</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0524</v>
+        <v>-0.3447</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.5743</v>
+        <v>-5.3098</v>
       </c>
       <c r="G18" t="n">
         <v>-4.715</v>
@@ -1858,13 +1858,13 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3144</v>
+        <v>1.2866</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3978</v>
+        <v>1.1055</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0835</v>
+        <v>0.1811</v>
       </c>
       <c r="V18" t="n">
         <v>-2.7922</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.7053</v>
+        <v>-5.9992</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.6304</v>
+        <v>-4.9484</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0749</v>
+        <v>-1.0508</v>
       </c>
       <c r="G19" t="n">
         <v>-5.0328</v>
@@ -1936,13 +1936,13 @@
         <v>3.0192</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3892</v>
+        <v>0.317</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.749</v>
+        <v>-0.067</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3598</v>
+        <v>0.3839</v>
       </c>
       <c r="V19" t="n">
         <v>0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-25.558</v>
+        <v>-24.9084</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.644299999999999</v>
+        <v>-6.6444</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.9135</v>
+        <v>-18.2639</v>
       </c>
       <c r="G20" t="n">
         <v>-21.9066</v>
@@ -1990,10 +1990,10 @@
         <v>3.476099999999998</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01550000000000029</v>
+        <v>0.01550000000000074</v>
       </c>
       <c r="L20" t="n">
-        <v>3.461</v>
+        <v>3.461000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>-25.3829</v>
@@ -2014,13 +2014,13 @@
         <v>15.096</v>
       </c>
       <c r="S20" t="n">
-        <v>6.3867</v>
+        <v>7.0364</v>
       </c>
       <c r="T20" t="n">
-        <v>5.410500000000001</v>
+        <v>5.4104</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9762</v>
+        <v>1.6256</v>
       </c>
       <c r="V20" t="n">
         <v>-5.320599999999999</v>
